--- a/Reporte_Final_Pruebas_Nexus.xlsx
+++ b/Reporte_Final_Pruebas_Nexus.xlsx
@@ -61,10 +61,10 @@
     <t>registra un nuevo Padawan correctamente</t>
   </si>
   <si>
-    <t>Ejecuta la validación del escenario descrito aplicando Caja Negra/Blanca. Aserciona los flujos de ejecución de código, verifica la consistencia del estado interno y asegura el cumplimiento estricto del contrato técnico.</t>
-  </si>
-  <si>
-    <t>Mantiene la calidad general del producto de software. Su correcta ejecución previene defectos en producción que costarían tiempo valioso y afectarían negativamente la confianza del cliente.</t>
+    <t>Ejecuta una verificación automática para confirmar que esta pequeña pieza de la aplicación cumpla su tarea de forma exacta, tal como fue diseñada.</t>
+  </si>
+  <si>
+    <t>Previene que pequeños defectos internos lleguen al cliente final, ahorrando a la empresa los enormes costos de reparar software una vez que ya está público.</t>
   </si>
   <si>
     <t>PASSED</t>
@@ -76,10 +76,10 @@
     <t>retorna 409 cuando el email ya existe</t>
   </si>
   <si>
-    <t>Ejecuta pruebas de carga y concurrencia empleando Caja Negra/Blanca. Simula múltiples hilos virtuales para saturar el pool de conexiones y evaluar la latencia y rendimiento del servidor bajo presión.</t>
-  </si>
-  <si>
-    <t>Asegura que el sistema soporte picos de tráfico comercial. Previene caídas durante campañas de marketing importantes, garantizando una experiencia de usuario fluida y constante.</t>
+    <t>Simula la entrada masiva de miles de usuarios al mismo tiempo para medir si los servidores soportan la presión sin ponerse lentos o apagarse.</t>
+  </si>
+  <si>
+    <t>Asegura que en días de alta demanda comercial (como campañas publicitarias) la plataforma no colapse, protegiendo las ventas y la reputación de la empresa.</t>
   </si>
   <si>
     <t>3</t>
@@ -106,10 +106,10 @@
     <t>retorna datos del usuario autenticado</t>
   </si>
   <si>
-    <t>Examina el sistema de vacantes usando Caja Negra/Blanca. Verifica consultas SQL complejas, índices de búsqueda y paginación de resultados, asegurando tiempos de respuesta óptimos bajo alta carga de peticiones.</t>
-  </si>
-  <si>
-    <t>Soporta el modelo de negocio central de reclutamiento. Un sistema de búsqueda rápido conecta talento con empresas, generando valor directo e incrementando monetización.</t>
+    <t>Comprueba que las funciones principales del producto (como ver gráficas o buscar información) operen correctamente y muestren datos precisos al usuario.</t>
+  </si>
+  <si>
+    <t>Asegura que el producto entregue el valor prometido al cliente. Si esta función falla, los clientes dejarán de pagar por la plataforma.</t>
   </si>
   <si>
     <t>7</t>
@@ -118,10 +118,10 @@
     <t>retorna 401 sin token</t>
   </si>
   <si>
-    <t>Analiza flujos de autenticación usando Caja Negra/Blanca. Valida tokens JWT, cifrado bcrypt de contraseñas y manejo de sesiones HTTP para garantizar el control de acceso seguro y evitar intrusiones.</t>
-  </si>
-  <si>
-    <t>Asegura la protección de datos confidenciales del cliente. Mitiga riesgos legales y financieros asociados con brechas de seguridad y asegura el cumplimiento de normativas de privacidad.</t>
+    <t>Revisa los candados de seguridad simulando intentos de ingreso (correctos e incorrectos) para confirmar que el sistema reconoce quién puede entrar y quién no.</t>
+  </si>
+  <si>
+    <t>Protege la privacidad de los usuarios, asegurando que nadie pueda robar información confidencial ni entrar a cuentas que no le pertenecen.</t>
   </si>
   <si>
     <t>ia.test.ts</t>
@@ -460,10 +460,10 @@
     <t>UNIT-AUTH-SCH-18: rechaza nombres como numero</t>
   </si>
   <si>
-    <t>Verifica la respuesta HTTP del endpoint mediante Caja Negra/Blanca. Evalúa los códigos de estado y latencia de red asegurando que la infraestructura base del servicio opere correctamente sin interrupciones.</t>
-  </si>
-  <si>
-    <t>Garantiza la disponibilidad continua de la plataforma para los clientes. Previene interrupciones prolongadas que pueden generar pérdidas financieras, dañar la reputación y afectar los SLAs.</t>
+    <t>Hace una revisión rápida de las conexiones principales del sistema para asegurar que la comunicación entre el usuario y nuestros servidores funciona sin problemas.</t>
+  </si>
+  <si>
+    <t>Funciona como una alarma temprana. Nos asegura que el sistema está 'vivo' y disponible para que ningún cliente se quede sin servicio de imprevisto.</t>
   </si>
   <si>
     <t>19</t>
@@ -2721,10 +2721,10 @@
         <v>50</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>15</v>
@@ -3221,10 +3221,10 @@
         <v>77</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>15</v>
@@ -3486,10 +3486,10 @@
         <v>90</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>15</v>
@@ -3506,10 +3506,10 @@
         <v>92</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>15</v>
@@ -3526,10 +3526,10 @@
         <v>94</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>15</v>
@@ -3546,10 +3546,10 @@
         <v>96</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
@@ -3566,10 +3566,10 @@
         <v>98</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -3586,10 +3586,10 @@
         <v>100</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>15</v>
@@ -3766,10 +3766,10 @@
         <v>110</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>15</v>
@@ -3786,10 +3786,10 @@
         <v>111</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>15</v>
@@ -3806,10 +3806,10 @@
         <v>112</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>15</v>
@@ -3826,10 +3826,10 @@
         <v>113</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>15</v>
@@ -4166,10 +4166,10 @@
         <v>132</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>15</v>
@@ -4186,10 +4186,10 @@
         <v>133</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>15</v>
@@ -4206,10 +4206,10 @@
         <v>134</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>15</v>
@@ -4226,10 +4226,10 @@
         <v>135</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>15</v>
@@ -4246,10 +4246,10 @@
         <v>136</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>15</v>
@@ -4266,10 +4266,10 @@
         <v>137</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F54" s="10" t="s">
         <v>15</v>
@@ -4286,10 +4286,10 @@
         <v>139</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>15</v>
@@ -4306,10 +4306,10 @@
         <v>141</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>15</v>
@@ -4326,10 +4326,10 @@
         <v>143</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>15</v>
@@ -4626,10 +4626,10 @@
         <v>167</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>15</v>
@@ -4646,10 +4646,10 @@
         <v>168</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>15</v>
@@ -4666,10 +4666,10 @@
         <v>169</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>15</v>
@@ -4686,10 +4686,10 @@
         <v>170</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>15</v>
@@ -4706,10 +4706,10 @@
         <v>171</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>15</v>
@@ -4726,10 +4726,10 @@
         <v>172</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>15</v>
@@ -4746,10 +4746,10 @@
         <v>173</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F78" s="10" t="s">
         <v>15</v>
@@ -4766,10 +4766,10 @@
         <v>174</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>15</v>
@@ -4786,10 +4786,10 @@
         <v>175</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>15</v>
@@ -5206,10 +5206,10 @@
         <v>203</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>15</v>
@@ -5226,10 +5226,10 @@
         <v>204</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F102" s="10" t="s">
         <v>15</v>
@@ -5246,10 +5246,10 @@
         <v>205</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>15</v>
@@ -5266,10 +5266,10 @@
         <v>206</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F104" s="10" t="s">
         <v>15</v>
@@ -5286,10 +5286,10 @@
         <v>207</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>15</v>
@@ -5306,10 +5306,10 @@
         <v>208</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F106" s="10" t="s">
         <v>15</v>
@@ -5326,10 +5326,10 @@
         <v>209</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>15</v>
@@ -5346,10 +5346,10 @@
         <v>210</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F108" s="10" t="s">
         <v>15</v>
@@ -5366,10 +5366,10 @@
         <v>211</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>15</v>
@@ -5606,10 +5606,10 @@
         <v>224</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>15</v>
@@ -5626,10 +5626,10 @@
         <v>225</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F122" s="10" t="s">
         <v>15</v>
@@ -5646,10 +5646,10 @@
         <v>226</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>15</v>
@@ -5666,10 +5666,10 @@
         <v>227</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F124" s="10" t="s">
         <v>15</v>
@@ -5686,10 +5686,10 @@
         <v>228</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>15</v>
@@ -5706,10 +5706,10 @@
         <v>229</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F126" s="10" t="s">
         <v>15</v>
@@ -5726,10 +5726,10 @@
         <v>230</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>15</v>
@@ -5746,10 +5746,10 @@
         <v>231</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F128" s="10" t="s">
         <v>15</v>
@@ -5766,10 +5766,10 @@
         <v>232</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>15</v>
@@ -6026,10 +6026,10 @@
         <v>246</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F142" s="10" t="s">
         <v>15</v>
@@ -6046,10 +6046,10 @@
         <v>247</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>15</v>
@@ -6066,10 +6066,10 @@
         <v>248</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F144" s="10" t="s">
         <v>15</v>
@@ -6086,10 +6086,10 @@
         <v>249</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>15</v>
@@ -6106,10 +6106,10 @@
         <v>250</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F146" s="10" t="s">
         <v>15</v>
@@ -6126,10 +6126,10 @@
         <v>251</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>15</v>
@@ -6146,10 +6146,10 @@
         <v>252</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F148" s="10" t="s">
         <v>15</v>
@@ -6166,10 +6166,10 @@
         <v>253</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>15</v>
@@ -6186,10 +6186,10 @@
         <v>254</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F150" s="10" t="s">
         <v>15</v>
@@ -6386,10 +6386,10 @@
         <v>265</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F160" s="10" t="s">
         <v>15</v>
@@ -6406,10 +6406,10 @@
         <v>266</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>15</v>
@@ -6426,10 +6426,10 @@
         <v>267</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F162" s="10" t="s">
         <v>15</v>
@@ -6446,10 +6446,10 @@
         <v>268</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>15</v>
@@ -6466,10 +6466,10 @@
         <v>269</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F164" s="10" t="s">
         <v>15</v>
@@ -6486,10 +6486,10 @@
         <v>270</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>15</v>
@@ -6506,10 +6506,10 @@
         <v>271</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F166" s="10" t="s">
         <v>15</v>
@@ -6771,10 +6771,10 @@
         <v>284</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>15</v>
@@ -6791,10 +6791,10 @@
         <v>285</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>15</v>
@@ -6811,10 +6811,10 @@
         <v>286</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>15</v>
@@ -6831,10 +6831,10 @@
         <v>287</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
@@ -6851,10 +6851,10 @@
         <v>288</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -6871,10 +6871,10 @@
         <v>289</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>15</v>
@@ -6891,10 +6891,10 @@
         <v>290</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>15</v>
@@ -6911,10 +6911,10 @@
         <v>291</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>15</v>
@@ -6931,10 +6931,10 @@
         <v>292</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>15</v>
@@ -7371,10 +7371,10 @@
         <v>316</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>15</v>
@@ -7391,10 +7391,10 @@
         <v>317</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>15</v>
@@ -7411,10 +7411,10 @@
         <v>318</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>15</v>
@@ -7431,10 +7431,10 @@
         <v>319</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>15</v>
@@ -7451,10 +7451,10 @@
         <v>320</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>15</v>
@@ -7471,10 +7471,10 @@
         <v>321</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>15</v>
@@ -7491,10 +7491,10 @@
         <v>322</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>15</v>
@@ -7756,10 +7756,10 @@
         <v>335</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>15</v>
@@ -7776,10 +7776,10 @@
         <v>336</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>15</v>
@@ -7796,10 +7796,10 @@
         <v>337</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>15</v>
@@ -7816,10 +7816,10 @@
         <v>338</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
@@ -7836,10 +7836,10 @@
         <v>339</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -7856,10 +7856,10 @@
         <v>340</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>15</v>
@@ -7876,10 +7876,10 @@
         <v>341</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>15</v>
@@ -7896,10 +7896,10 @@
         <v>342</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>15</v>
@@ -7916,10 +7916,10 @@
         <v>343</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>15</v>
@@ -8356,10 +8356,10 @@
         <v>366</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>15</v>
@@ -8376,10 +8376,10 @@
         <v>367</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>15</v>
@@ -8396,10 +8396,10 @@
         <v>368</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>15</v>
@@ -8416,10 +8416,10 @@
         <v>369</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>15</v>
@@ -8436,10 +8436,10 @@
         <v>370</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>15</v>
@@ -8456,10 +8456,10 @@
         <v>371</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>15</v>
@@ -8476,10 +8476,10 @@
         <v>372</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>15</v>
@@ -8741,10 +8741,10 @@
         <v>385</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>15</v>
@@ -8761,10 +8761,10 @@
         <v>386</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>15</v>
@@ -8781,10 +8781,10 @@
         <v>387</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>15</v>
@@ -8801,10 +8801,10 @@
         <v>388</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
@@ -8821,10 +8821,10 @@
         <v>389</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -8841,10 +8841,10 @@
         <v>390</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>15</v>
@@ -8861,10 +8861,10 @@
         <v>391</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>15</v>
@@ -8881,10 +8881,10 @@
         <v>392</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>15</v>
@@ -8901,10 +8901,10 @@
         <v>393</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>15</v>
@@ -9341,10 +9341,10 @@
         <v>416</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>15</v>
@@ -9361,10 +9361,10 @@
         <v>417</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>15</v>
@@ -9381,10 +9381,10 @@
         <v>418</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>15</v>
@@ -9401,10 +9401,10 @@
         <v>419</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>15</v>
@@ -9421,10 +9421,10 @@
         <v>420</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>15</v>
@@ -9441,10 +9441,10 @@
         <v>421</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>15</v>
@@ -9461,10 +9461,10 @@
         <v>422</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>15</v>
@@ -9726,10 +9726,10 @@
         <v>435</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>15</v>
@@ -9746,10 +9746,10 @@
         <v>436</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>15</v>
@@ -9766,10 +9766,10 @@
         <v>437</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>15</v>
@@ -9786,10 +9786,10 @@
         <v>438</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
@@ -9806,10 +9806,10 @@
         <v>439</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -9826,10 +9826,10 @@
         <v>440</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>15</v>
@@ -9846,10 +9846,10 @@
         <v>441</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>15</v>
@@ -9866,10 +9866,10 @@
         <v>442</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>15</v>
@@ -9886,10 +9886,10 @@
         <v>443</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>15</v>
@@ -10326,10 +10326,10 @@
         <v>466</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>15</v>
@@ -10346,10 +10346,10 @@
         <v>467</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>15</v>
@@ -10366,10 +10366,10 @@
         <v>468</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>15</v>
@@ -10386,10 +10386,10 @@
         <v>469</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>15</v>
@@ -10406,10 +10406,10 @@
         <v>470</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>15</v>
@@ -10426,10 +10426,10 @@
         <v>471</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>15</v>
@@ -10446,10 +10446,10 @@
         <v>472</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>15</v>
@@ -10711,10 +10711,10 @@
         <v>485</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>15</v>
@@ -10731,10 +10731,10 @@
         <v>486</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>15</v>
@@ -10751,10 +10751,10 @@
         <v>487</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>15</v>
@@ -10771,10 +10771,10 @@
         <v>488</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
@@ -10791,10 +10791,10 @@
         <v>489</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -10811,10 +10811,10 @@
         <v>490</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>15</v>
@@ -10831,10 +10831,10 @@
         <v>491</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>15</v>
@@ -11011,10 +11011,10 @@
         <v>501</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>15</v>
@@ -11031,10 +11031,10 @@
         <v>502</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>15</v>
@@ -11051,10 +11051,10 @@
         <v>503</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>15</v>
@@ -11071,10 +11071,10 @@
         <v>504</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>15</v>
@@ -11091,10 +11091,10 @@
         <v>505</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>15</v>
@@ -11111,10 +11111,10 @@
         <v>506</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>15</v>
@@ -11131,10 +11131,10 @@
         <v>507</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>15</v>
@@ -11456,10 +11456,10 @@
         <v>524</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
@@ -11476,10 +11476,10 @@
         <v>525</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>15</v>
@@ -11496,10 +11496,10 @@
         <v>526</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>15</v>
@@ -11516,10 +11516,10 @@
         <v>527</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>15</v>
@@ -11536,10 +11536,10 @@
         <v>528</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>15</v>
@@ -11556,10 +11556,10 @@
         <v>529</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>15</v>
@@ -11576,10 +11576,10 @@
         <v>530</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>15</v>
@@ -12296,10 +12296,10 @@
         <v>522</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>15</v>
@@ -12316,10 +12316,10 @@
         <v>523</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>15</v>
@@ -12336,10 +12336,10 @@
         <v>524</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>15</v>
@@ -12356,10 +12356,10 @@
         <v>525</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>15</v>
@@ -12376,10 +12376,10 @@
         <v>526</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>15</v>
@@ -12396,10 +12396,10 @@
         <v>527</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>15</v>
@@ -12416,10 +12416,10 @@
         <v>528</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F66" s="10" t="s">
         <v>15</v>
@@ -12436,10 +12436,10 @@
         <v>529</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>15</v>
@@ -12456,10 +12456,10 @@
         <v>530</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F68" s="10" t="s">
         <v>15</v>
